--- a/templates/Directory-100.xlsx
+++ b/templates/Directory-100.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joseph\Downloads\_sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CC8E8E7-C5DF-4918-B28D-47D0A73F29E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D50E739-8EA8-4195-8AC4-19B1727893FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Directory of Participants" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="60">
   <si>
     <t>Directory of Participants</t>
   </si>
@@ -122,13 +122,7 @@
     <t> PREPARED BY:</t>
   </si>
   <si>
-    <t>Training Assistant</t>
-  </si>
-  <si>
     <t>NOTED BY:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Traiing Manager </t>
   </si>
   <si>
     <t>[INSERT OSNET/STO  HEADER WITH LOGO HERE]</t>
@@ -144,9 +138,6 @@
   </si>
   <si>
     <t>Prepared by:</t>
-  </si>
-  <si>
-    <t>Michelle M. Saclet</t>
   </si>
   <si>
     <t>Date Prepared:</t>
@@ -210,6 +201,12 @@
   </si>
   <si>
     <t>Date Issued</t>
+  </si>
+  <si>
+    <t>Training Facilitator</t>
+  </si>
+  <si>
+    <t>Operations Manager</t>
   </si>
 </sst>
 </file>
@@ -4805,7 +4802,7 @@
       <c r="A120" s="1"/>
       <c r="B120" s="64"/>
       <c r="C120" s="2" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="D120" s="1"/>
       <c r="E120" s="1"/>
@@ -4860,7 +4857,7 @@
     <row r="122" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="1"/>
       <c r="B122" s="62" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C122" s="63"/>
       <c r="D122" s="1"/>
@@ -4890,7 +4887,7 @@
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="2" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D123" s="1"/>
       <c r="E123" s="1"/>
@@ -29513,7 +29510,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="87" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B1" s="88"/>
       <c r="C1" s="88"/>
@@ -29599,7 +29596,7 @@
     </row>
     <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="105" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4" s="88"/>
       <c r="C4" s="88"/>
@@ -29647,10 +29644,10 @@
     <row r="7" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="66" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C8" s="106" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D8" s="98"/>
       <c r="E8" s="98"/>
@@ -29665,11 +29662,9 @@
     </row>
     <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="66" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
-      <c r="C9" s="106" t="s">
-        <v>39</v>
-      </c>
+      <c r="C9" s="106"/>
       <c r="D9" s="98"/>
       <c r="E9" s="98"/>
       <c r="F9" s="98"/>
@@ -29683,7 +29678,7 @@
     </row>
     <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="66" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C10" s="107"/>
       <c r="D10" s="98"/>
@@ -29711,28 +29706,28 @@
         <v>6</v>
       </c>
       <c r="B12" s="101" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C12" s="101" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D12" s="101" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E12" s="103" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F12" s="98"/>
       <c r="G12" s="98"/>
       <c r="H12" s="99"/>
       <c r="I12" s="104" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J12" s="98"/>
       <c r="K12" s="98"/>
       <c r="L12" s="99"/>
       <c r="M12" s="108" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="N12" s="31"/>
       <c r="O12" s="31"/>
@@ -29754,7 +29749,7 @@
       <c r="C13" s="102"/>
       <c r="D13" s="102"/>
       <c r="E13" s="69" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F13" s="69" t="s">
         <v>27</v>
@@ -29766,16 +29761,16 @@
         <v>14</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J13" s="16" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="M13" s="102"/>
       <c r="N13" s="31"/>
@@ -31632,7 +31627,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="109" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B1" s="88"/>
       <c r="C1" s="88"/>
@@ -31691,7 +31686,7 @@
     </row>
     <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="77" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C5" s="110"/>
       <c r="D5" s="98"/>
@@ -31699,7 +31694,7 @@
     </row>
     <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="77" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C6" s="110"/>
       <c r="D6" s="98"/>
@@ -31707,7 +31702,7 @@
     </row>
     <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="77" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C7" s="110"/>
       <c r="D7" s="98"/>
@@ -31719,16 +31714,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="78" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>10</v>
@@ -31737,31 +31732,31 @@
         <v>12</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="M9" s="11" t="s">
         <v>21</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O9" s="14" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="P9" s="14" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="Q9" s="79"/>
       <c r="R9" s="79"/>
